--- a/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_david313-315(4).xlsx
+++ b/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_david313-315(4).xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Unity Projects\VNovelizerTest_v1.0\Assets\Resources\VNovelizerRes\ExcelVNScripts\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
@@ -29,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1301" uniqueCount="457">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1302" uniqueCount="463">
   <si>
     <t>ID</t>
   </si>
@@ -79,6 +84,9 @@
     <t/>
   </si>
   <si>
+    <t>stop</t>
+  </si>
+  <si>
     <t>false</t>
   </si>
   <si>
@@ -109,6 +117,9 @@
     <t>看着证件上姐姐舒展的笑颜，一股前所未有的使命感在你胸中油然而生。无论前路上的阴霾多么厚重，她永远是那个会提着摄像机，冲在第一线，用快门和录音笔带回真相的人。</t>
   </si>
   <si>
+    <t>16 enhanced_suspence</t>
+  </si>
+  <si>
     <t>源类型=type:txt_pb; 层级=3; 选项/备注=保持怀疑，或许能从中找到真相</t>
   </si>
   <si>
@@ -289,6 +300,9 @@
     <t>在思绪尚未从震惊中回神之前，你的指尖已猛地发力，将那张刻有你姓氏的卡片从床底的黑暗中抢了出来，带起一大片呛人的灰絮。浓重的焦黑在你用力地擦拭下一点点散开，露出和姐姐当初跌落的那道栏杆同样的青蓝。</t>
   </si>
   <si>
+    <t>17 enhanced_suspense-tense-background-music</t>
+  </si>
+  <si>
     <t>源类型=type:txt_pb; 层级=21</t>
   </si>
   <si>
@@ -310,6 +324,9 @@
     <t>black</t>
   </si>
   <si>
+    <t>playsfx(EarRinging)</t>
+  </si>
+  <si>
     <t>源类型=type:txt_pb; 层级=23</t>
   </si>
   <si>
@@ -541,7 +558,7 @@
     <t>50</t>
   </si>
   <si>
-    <t>时间停在了这里，像是被插入的针头钉在了你的血液之中，，唯留皮肤被刺穿的余响如耳鸣般在你脑中回荡。</t>
+    <t>时间停在了这里，像是被插入的针头钉在了你的血液之中，唯留皮肤被刺穿的余响如耳鸣般在你脑中回荡。</t>
   </si>
   <si>
     <t>源类型=type:txt_pb; 层级=48</t>
@@ -571,6 +588,9 @@
     <t>你下意识地活动了一下身体，确认它还听从你意识的指挥，那片眩晕的迷晕还在太阳穴附近弥漫着，像一支渐熄的蜡烛，带来一阵阵火辣辣的灼痛。</t>
   </si>
   <si>
+    <t>3 enhanced leberch-horror-night</t>
+  </si>
+  <si>
     <t>源类型=type:txt_pb; 层级=51</t>
   </si>
   <si>
@@ -671,6 +691,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t>loadScript(</t>
     </r>
     <r>
@@ -880,13 +905,21 @@
     <t>随着屏幕的自动熄灭，大卫心中的最后一丝执念也溶解在了浓稠的夜色中。当他重新将手电的光柱对准了病房门口，一阵微弱的电磁轻响从墙壁的一侧滑了进来，在刺鼻的空气中荡开一圈涟漪。</t>
   </si>
   <si>
+    <t>这是来自医院广播的调谐信号，此时被启动只能说明一件事——有除了你们之外的人躲在控制室里。</t>
+  </si>
+  <si>
     <t>91</t>
   </si>
   <si>
-    <t>随着一声仿佛用于吸引你们注意力的高亢嗡鸣自墙壁内响起，你很快意识到这是来自医院广播的调谐信号。尖锐的嗡鸣才褪去不到两秒，一阵令人毛骨悚然的掌声急不可耐地取而代之。</t>
+    <t>只听高亢的啸叫过后，一阵令人毛骨悚然的掌声急不可耐地从音频中响起，像是一场大戏的开场礼。</t>
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t>loadScript(</t>
     </r>
     <r>
@@ -1484,6 +1517,11 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1636,11 +1674,6 @@
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="宋体"/>
-      <charset val="134"/>
     </font>
   </fonts>
   <fills count="34">
@@ -1949,31 +1982,28 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1982,124 +2012,130 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -2637,7 +2673,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L91"/>
+  <dimension ref="A1:L92"/>
   <sheetFormatPr defaultColWidth="10.2857142857143" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -2711,21 +2747,21 @@
         <v>15</v>
       </c>
       <c r="I2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" ht="30" spans="1:12">
       <c r="A3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B3" t="s">
         <v>13</v>
@@ -2755,15 +2791,15 @@
         <v>15</v>
       </c>
       <c r="K3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B4" t="s">
         <v>13</v>
@@ -2796,12 +2832,12 @@
         <v>15</v>
       </c>
       <c r="L4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" ht="54" spans="1:12">
       <c r="A5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B5" t="s">
         <v>13</v>
@@ -2819,11 +2855,10 @@
         <v>15</v>
       </c>
       <c r="G5" t="s">
-        <v>25</v>
-      </c>
-      <c r="H5"/>
+        <v>26</v>
+      </c>
       <c r="I5" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="J5" t="s">
         <v>15</v>
@@ -2832,12 +2867,12 @@
         <v>15</v>
       </c>
       <c r="L5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" ht="54" spans="1:12">
       <c r="A6" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B6" t="s">
         <v>13</v>
@@ -2855,7 +2890,7 @@
         <v>15</v>
       </c>
       <c r="G6" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H6" t="s">
         <v>15</v>
@@ -2870,12 +2905,12 @@
         <v>15</v>
       </c>
       <c r="L6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7" ht="40.5" spans="1:12">
       <c r="A7" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B7" t="s">
         <v>13</v>
@@ -2893,7 +2928,7 @@
         <v>15</v>
       </c>
       <c r="G7" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H7" t="s">
         <v>15</v>
@@ -2908,15 +2943,15 @@
         <v>15</v>
       </c>
       <c r="L7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" ht="27" spans="1:12">
       <c r="A8" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C8" t="s">
         <v>14</v>
@@ -2931,7 +2966,7 @@
         <v>15</v>
       </c>
       <c r="G8" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H8" t="s">
         <v>15</v>
@@ -2946,12 +2981,12 @@
         <v>15</v>
       </c>
       <c r="L8" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9" ht="27" spans="1:12">
       <c r="A9" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B9" t="s">
         <v>13</v>
@@ -2959,7 +2994,6 @@
       <c r="C9" t="s">
         <v>14</v>
       </c>
-      <c r="D9"/>
       <c r="E9" t="s">
         <v>15</v>
       </c>
@@ -2967,7 +3001,7 @@
         <v>15</v>
       </c>
       <c r="G9" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H9" t="s">
         <v>15</v>
@@ -2979,21 +3013,21 @@
         <v>15</v>
       </c>
       <c r="L9" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10" ht="30" spans="1:12">
       <c r="A10" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B10" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C10" t="s">
         <v>14</v>
       </c>
       <c r="D10" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E10" t="s">
         <v>15</v>
@@ -3002,7 +3036,7 @@
         <v>15</v>
       </c>
       <c r="G10" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H10" t="s">
         <v>15</v>
@@ -3014,15 +3048,15 @@
         <v>15</v>
       </c>
       <c r="K10" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="L10" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11" ht="30" spans="1:12">
       <c r="A11" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B11" t="s">
         <v>13</v>
@@ -3031,7 +3065,7 @@
         <v>14</v>
       </c>
       <c r="D11" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E11" t="s">
         <v>15</v>
@@ -3040,7 +3074,7 @@
         <v>15</v>
       </c>
       <c r="G11" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="H11" t="s">
         <v>15</v>
@@ -3055,21 +3089,21 @@
         <v>15</v>
       </c>
       <c r="L11" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12" ht="55.5" spans="1:12">
       <c r="A12" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B12" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C12" t="s">
         <v>14</v>
       </c>
       <c r="D12" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E12" t="s">
         <v>15</v>
@@ -3078,7 +3112,7 @@
         <v>15</v>
       </c>
       <c r="G12" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H12" t="s">
         <v>15</v>
@@ -3093,12 +3127,12 @@
         <v>15</v>
       </c>
       <c r="L12" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13" ht="57" spans="1:12">
       <c r="A13" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B13" t="s">
         <v>13</v>
@@ -3107,7 +3141,7 @@
         <v>14</v>
       </c>
       <c r="D13" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E13" t="s">
         <v>15</v>
@@ -3116,7 +3150,7 @@
         <v>15</v>
       </c>
       <c r="G13" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="H13" t="s">
         <v>15</v>
@@ -3128,15 +3162,15 @@
         <v>15</v>
       </c>
       <c r="K13" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="L13" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="14" ht="42" spans="1:12">
       <c r="A14" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B14" t="s">
         <v>13</v>
@@ -3154,7 +3188,7 @@
         <v>15</v>
       </c>
       <c r="G14" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="H14" t="s">
         <v>15</v>
@@ -3169,15 +3203,15 @@
         <v>15</v>
       </c>
       <c r="L14" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15" ht="40.5" spans="1:12">
       <c r="A15" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B15" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C15" t="s">
         <v>14</v>
@@ -3192,7 +3226,7 @@
         <v>15</v>
       </c>
       <c r="G15" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H15" t="s">
         <v>15</v>
@@ -3207,12 +3241,12 @@
         <v>15</v>
       </c>
       <c r="L15" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="16" spans="1:12">
       <c r="A16" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B16" t="s">
         <v>13</v>
@@ -3230,7 +3264,7 @@
         <v>15</v>
       </c>
       <c r="G16" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H16" t="s">
         <v>15</v>
@@ -3245,15 +3279,15 @@
         <v>15</v>
       </c>
       <c r="L16" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17" spans="1:12">
       <c r="A17" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B17" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C17" t="s">
         <v>14</v>
@@ -3268,7 +3302,7 @@
         <v>15</v>
       </c>
       <c r="G17" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="H17" t="s">
         <v>15</v>
@@ -3283,12 +3317,12 @@
         <v>15</v>
       </c>
       <c r="L17" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="18" ht="40.5" spans="1:12">
       <c r="A18" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B18" t="s">
         <v>13</v>
@@ -3306,7 +3340,7 @@
         <v>15</v>
       </c>
       <c r="G18" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H18" t="s">
         <v>15</v>
@@ -3321,12 +3355,12 @@
         <v>15</v>
       </c>
       <c r="L18" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="19" ht="54" spans="1:12">
       <c r="A19" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B19" t="s">
         <v>13</v>
@@ -3344,7 +3378,7 @@
         <v>15</v>
       </c>
       <c r="G19" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H19" t="s">
         <v>15</v>
@@ -3356,15 +3390,15 @@
         <v>15</v>
       </c>
       <c r="K19" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="L19" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="20" ht="40.5" spans="1:12">
       <c r="A20" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B20" t="s">
         <v>13</v>
@@ -3382,7 +3416,7 @@
         <v>15</v>
       </c>
       <c r="G20" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H20" t="s">
         <v>15</v>
@@ -3397,12 +3431,12 @@
         <v>15</v>
       </c>
       <c r="L20" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="21" ht="57" spans="1:12">
       <c r="A21" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B21" t="s">
         <v>13</v>
@@ -3420,14 +3454,11 @@
         <v>15</v>
       </c>
       <c r="G21" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H21" t="s">
         <v>15</v>
       </c>
-      <c r="I21" t="s">
-        <v>15</v>
-      </c>
       <c r="J21" t="s">
         <v>15</v>
       </c>
@@ -3435,15 +3466,15 @@
         <v>15</v>
       </c>
       <c r="L21" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="22" spans="1:12">
       <c r="A22" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B22" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C22" t="s">
         <v>14</v>
@@ -3458,13 +3489,13 @@
         <v>15</v>
       </c>
       <c r="G22" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H22" t="s">
         <v>15</v>
       </c>
       <c r="I22" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J22" t="s">
         <v>15</v>
@@ -3473,12 +3504,12 @@
         <v>15</v>
       </c>
       <c r="L22" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="23" ht="67.5" spans="1:12">
       <c r="A23" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B23" t="s">
         <v>13</v>
@@ -3496,13 +3527,13 @@
         <v>15</v>
       </c>
       <c r="G23" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H23" t="s">
         <v>15</v>
       </c>
       <c r="I23" t="s">
-        <v>15</v>
+        <v>88</v>
       </c>
       <c r="J23" t="s">
         <v>15</v>
@@ -3511,12 +3542,12 @@
         <v>15</v>
       </c>
       <c r="L23" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="24" ht="30" spans="1:12">
       <c r="A24" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B24" t="s">
         <v>13</v>
@@ -3534,7 +3565,7 @@
         <v>15</v>
       </c>
       <c r="G24" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="H24" t="s">
         <v>15</v>
@@ -3549,12 +3580,12 @@
         <v>15</v>
       </c>
       <c r="L24" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="25" spans="1:12">
       <c r="A25" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B25" t="s">
         <v>13</v>
@@ -3572,10 +3603,10 @@
         <v>15</v>
       </c>
       <c r="G25" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="H25" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="I25" t="s">
         <v>15</v>
@@ -3584,15 +3615,15 @@
         <v>15</v>
       </c>
       <c r="K25" t="s">
-        <v>15</v>
+        <v>96</v>
       </c>
       <c r="L25" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
     </row>
     <row r="26" ht="54" spans="1:12">
       <c r="A26" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="B26" t="s">
         <v>13</v>
@@ -3610,7 +3641,7 @@
         <v>15</v>
       </c>
       <c r="G26" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="H26" t="s">
         <v>15</v>
@@ -3625,12 +3656,12 @@
         <v>15</v>
       </c>
       <c r="L26" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
     </row>
     <row r="27" ht="69" spans="1:12">
       <c r="A27" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="B27" t="s">
         <v>13</v>
@@ -3648,7 +3679,7 @@
         <v>15</v>
       </c>
       <c r="G27" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="H27" t="s">
         <v>15</v>
@@ -3660,15 +3691,15 @@
         <v>15</v>
       </c>
       <c r="K27" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="L27" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
     </row>
     <row r="28" ht="40.5" spans="1:12">
       <c r="A28" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B28" t="s">
         <v>13</v>
@@ -3686,7 +3717,7 @@
         <v>15</v>
       </c>
       <c r="G28" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="H28" t="s">
         <v>15</v>
@@ -3701,12 +3732,12 @@
         <v>15</v>
       </c>
       <c r="L28" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
     </row>
     <row r="29" ht="67.5" spans="1:12">
       <c r="A29" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="B29" t="s">
         <v>13</v>
@@ -3724,7 +3755,7 @@
         <v>15</v>
       </c>
       <c r="G29" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="H29" t="s">
         <v>15</v>
@@ -3739,12 +3770,12 @@
         <v>15</v>
       </c>
       <c r="L29" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
     </row>
     <row r="30" ht="28.5" spans="1:12">
       <c r="A30" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="B30" t="s">
         <v>13</v>
@@ -3762,7 +3793,7 @@
         <v>15</v>
       </c>
       <c r="G30" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="H30" t="s">
         <v>15</v>
@@ -3777,12 +3808,12 @@
         <v>15</v>
       </c>
       <c r="L30" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
     </row>
     <row r="31" ht="54" spans="1:12">
       <c r="A31" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="B31" t="s">
         <v>13</v>
@@ -3800,7 +3831,7 @@
         <v>15</v>
       </c>
       <c r="G31" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="H31" t="s">
         <v>15</v>
@@ -3815,12 +3846,12 @@
         <v>15</v>
       </c>
       <c r="L31" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
     </row>
     <row r="32" ht="42" spans="1:12">
       <c r="A32" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="B32" t="s">
         <v>13</v>
@@ -3838,7 +3869,7 @@
         <v>15</v>
       </c>
       <c r="G32" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="H32" t="s">
         <v>15</v>
@@ -3853,12 +3884,12 @@
         <v>15</v>
       </c>
       <c r="L32" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
     </row>
     <row r="33" spans="1:12">
       <c r="A33" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="B33" t="s">
         <v>13</v>
@@ -3876,7 +3907,7 @@
         <v>15</v>
       </c>
       <c r="G33" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="H33" t="s">
         <v>15</v>
@@ -3888,15 +3919,15 @@
         <v>15</v>
       </c>
       <c r="K33" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="L33" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
     </row>
     <row r="34" ht="40.5" spans="1:12">
       <c r="A34" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B34" t="s">
         <v>13</v>
@@ -3914,7 +3945,7 @@
         <v>15</v>
       </c>
       <c r="G34" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="H34" t="s">
         <v>15</v>
@@ -3929,12 +3960,12 @@
         <v>15</v>
       </c>
       <c r="L34" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="35" ht="40.5" spans="1:12">
       <c r="A35" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="B35" t="s">
         <v>13</v>
@@ -3952,7 +3983,7 @@
         <v>15</v>
       </c>
       <c r="G35" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="H35" t="s">
         <v>15</v>
@@ -3967,12 +3998,12 @@
         <v>15</v>
       </c>
       <c r="L35" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="36" spans="1:12">
       <c r="A36" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="B36" t="s">
         <v>13</v>
@@ -3990,7 +4021,7 @@
         <v>15</v>
       </c>
       <c r="G36" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="H36" t="s">
         <v>15</v>
@@ -4005,12 +4036,12 @@
         <v>15</v>
       </c>
       <c r="L36" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
     </row>
     <row r="37" ht="27" spans="1:12">
       <c r="A37" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B37" t="s">
         <v>13</v>
@@ -4028,7 +4059,7 @@
         <v>15</v>
       </c>
       <c r="G37" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H37" t="s">
         <v>15</v>
@@ -4043,12 +4074,12 @@
         <v>15</v>
       </c>
       <c r="L37" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
     </row>
     <row r="38" ht="60" spans="1:12">
       <c r="A38" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B38" t="s">
         <v>13</v>
@@ -4066,7 +4097,7 @@
         <v>15</v>
       </c>
       <c r="G38" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="H38" t="s">
         <v>15</v>
@@ -4081,12 +4112,12 @@
         <v>15</v>
       </c>
       <c r="L38" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
     </row>
     <row r="39" ht="40.5" spans="1:12">
       <c r="A39" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="B39" t="s">
         <v>13</v>
@@ -4104,7 +4135,7 @@
         <v>15</v>
       </c>
       <c r="G39" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="H39" t="s">
         <v>15</v>
@@ -4119,12 +4150,12 @@
         <v>15</v>
       </c>
       <c r="L39" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
     </row>
     <row r="40" ht="27" spans="1:12">
       <c r="A40" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B40" t="s">
         <v>13</v>
@@ -4142,7 +4173,7 @@
         <v>15</v>
       </c>
       <c r="G40" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="H40" t="s">
         <v>15</v>
@@ -4157,12 +4188,12 @@
         <v>15</v>
       </c>
       <c r="L40" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
     <row r="41" ht="43.5" spans="1:12">
       <c r="A41" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="B41" t="s">
         <v>13</v>
@@ -4180,7 +4211,7 @@
         <v>15</v>
       </c>
       <c r="G41" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="H41" t="s">
         <v>15</v>
@@ -4195,12 +4226,12 @@
         <v>15</v>
       </c>
       <c r="L41" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
     </row>
     <row r="42" ht="27" spans="1:12">
       <c r="A42" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="B42" t="s">
         <v>13</v>
@@ -4218,7 +4249,7 @@
         <v>15</v>
       </c>
       <c r="G42" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="H42" t="s">
         <v>15</v>
@@ -4233,12 +4264,12 @@
         <v>15</v>
       </c>
       <c r="L42" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
     </row>
     <row r="43" ht="30" spans="1:12">
       <c r="A43" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="B43" t="s">
         <v>13</v>
@@ -4256,7 +4287,7 @@
         <v>15</v>
       </c>
       <c r="G43" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="H43" t="s">
         <v>15</v>
@@ -4271,12 +4302,12 @@
         <v>15</v>
       </c>
       <c r="L43" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
     </row>
     <row r="44" ht="27" spans="1:12">
       <c r="A44" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="B44" t="s">
         <v>13</v>
@@ -4294,7 +4325,7 @@
         <v>15</v>
       </c>
       <c r="G44" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="H44" t="s">
         <v>15</v>
@@ -4309,12 +4340,12 @@
         <v>15</v>
       </c>
       <c r="L44" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="45" ht="57" spans="1:12">
       <c r="A45" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="B45" t="s">
         <v>13</v>
@@ -4332,7 +4363,7 @@
         <v>15</v>
       </c>
       <c r="G45" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H45" t="s">
         <v>15</v>
@@ -4347,12 +4378,12 @@
         <v>15</v>
       </c>
       <c r="L45" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
     </row>
     <row r="46" ht="54" spans="1:12">
       <c r="A46" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="B46" t="s">
         <v>13</v>
@@ -4370,7 +4401,7 @@
         <v>15</v>
       </c>
       <c r="G46" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="H46" t="s">
         <v>15</v>
@@ -4385,12 +4416,12 @@
         <v>15</v>
       </c>
       <c r="L46" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
     </row>
     <row r="47" ht="40.5" spans="1:12">
       <c r="A47" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="B47" t="s">
         <v>13</v>
@@ -4408,7 +4439,7 @@
         <v>15</v>
       </c>
       <c r="G47" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="H47" t="s">
         <v>15</v>
@@ -4423,12 +4454,12 @@
         <v>15</v>
       </c>
       <c r="L47" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
     </row>
     <row r="48" ht="54" spans="1:12">
       <c r="A48" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="B48" t="s">
         <v>13</v>
@@ -4446,7 +4477,7 @@
         <v>15</v>
       </c>
       <c r="G48" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="H48" t="s">
         <v>15</v>
@@ -4458,15 +4489,15 @@
         <v>15</v>
       </c>
       <c r="K48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="L48" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
     </row>
     <row r="49" spans="1:12">
       <c r="A49" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="B49" t="s">
         <v>13</v>
@@ -4484,7 +4515,7 @@
         <v>15</v>
       </c>
       <c r="G49" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="H49" t="s">
         <v>15</v>
@@ -4499,12 +4530,12 @@
         <v>15</v>
       </c>
       <c r="L49" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
     </row>
     <row r="50" ht="40.5" spans="1:12">
       <c r="A50" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="B50" t="s">
         <v>13</v>
@@ -4521,8 +4552,8 @@
       <c r="F50" t="s">
         <v>15</v>
       </c>
-      <c r="G50" t="s">
-        <v>170</v>
+      <c r="G50" s="2" t="s">
+        <v>174</v>
       </c>
       <c r="H50" t="s">
         <v>15</v>
@@ -4537,12 +4568,12 @@
         <v>15</v>
       </c>
       <c r="L50" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
     </row>
     <row r="51" ht="40.5" spans="1:12">
       <c r="A51" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="B51" t="s">
         <v>13</v>
@@ -4560,7 +4591,7 @@
         <v>15</v>
       </c>
       <c r="G51" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="H51" t="s">
         <v>15</v>
@@ -4575,12 +4606,12 @@
         <v>15</v>
       </c>
       <c r="L51" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
     </row>
     <row r="52" ht="67.5" spans="1:12">
       <c r="A52" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="B52" t="s">
         <v>13</v>
@@ -4598,14 +4629,12 @@
         <v>15</v>
       </c>
       <c r="G52" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="H52" t="s">
         <v>15</v>
       </c>
-      <c r="I52" t="s">
-        <v>15</v>
-      </c>
+      <c r="I52"/>
       <c r="J52" t="s">
         <v>15</v>
       </c>
@@ -4613,12 +4642,12 @@
         <v>15</v>
       </c>
       <c r="L52" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="53" ht="40.5" spans="1:12">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="53" ht="45" spans="1:12">
       <c r="A53" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="B53" t="s">
         <v>13</v>
@@ -4636,27 +4665,27 @@
         <v>15</v>
       </c>
       <c r="G53" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="H53" t="s">
         <v>15</v>
       </c>
       <c r="I53" t="s">
-        <v>15</v>
+        <v>184</v>
       </c>
       <c r="J53" t="s">
         <v>15</v>
       </c>
       <c r="K53" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L53" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
     </row>
     <row r="54" ht="67.5" spans="1:12">
       <c r="A54" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="B54" t="s">
         <v>13</v>
@@ -4674,7 +4703,7 @@
         <v>15</v>
       </c>
       <c r="G54" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="H54" t="s">
         <v>15</v>
@@ -4689,12 +4718,12 @@
         <v>15</v>
       </c>
       <c r="L54" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
     </row>
     <row r="55" ht="40.5" spans="1:12">
       <c r="A55" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="B55" t="s">
         <v>13</v>
@@ -4712,7 +4741,7 @@
         <v>15</v>
       </c>
       <c r="G55" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="H55" t="s">
         <v>15</v>
@@ -4727,15 +4756,15 @@
         <v>15</v>
       </c>
       <c r="L55" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
     </row>
     <row r="56" spans="1:12">
       <c r="A56" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="B56" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C56" t="s">
         <v>14</v>
@@ -4750,7 +4779,7 @@
         <v>15</v>
       </c>
       <c r="G56" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="H56" t="s">
         <v>15</v>
@@ -4765,21 +4794,21 @@
         <v>15</v>
       </c>
       <c r="L56" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
     </row>
     <row r="57" ht="30" spans="1:12">
       <c r="A57" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B57" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C57" t="s">
         <v>14</v>
       </c>
       <c r="D57" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E57" t="s">
         <v>15</v>
@@ -4788,7 +4817,7 @@
         <v>15</v>
       </c>
       <c r="G57" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="H57" t="s">
         <v>15</v>
@@ -4800,15 +4829,15 @@
         <v>15</v>
       </c>
       <c r="K57" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="L57" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
     </row>
     <row r="58" ht="69" spans="1:12">
       <c r="A58" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="B58" t="s">
         <v>13</v>
@@ -4817,7 +4846,7 @@
         <v>14</v>
       </c>
       <c r="D58" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E58" t="s">
         <v>15</v>
@@ -4826,7 +4855,7 @@
         <v>15</v>
       </c>
       <c r="G58" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="H58" t="s">
         <v>15</v>
@@ -4841,21 +4870,21 @@
         <v>15</v>
       </c>
       <c r="L58" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
     </row>
     <row r="59" ht="30" spans="1:12">
       <c r="A59" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="B59" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C59" t="s">
         <v>14</v>
       </c>
       <c r="D59" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E59" t="s">
         <v>15</v>
@@ -4864,7 +4893,7 @@
         <v>15</v>
       </c>
       <c r="G59" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="H59" t="s">
         <v>15</v>
@@ -4879,12 +4908,12 @@
         <v>15</v>
       </c>
       <c r="L59" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
     </row>
     <row r="60" ht="67.5" spans="1:12">
       <c r="A60" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="B60" t="s">
         <v>13</v>
@@ -4893,7 +4922,7 @@
         <v>14</v>
       </c>
       <c r="D60" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E60" t="s">
         <v>15</v>
@@ -4902,7 +4931,7 @@
         <v>15</v>
       </c>
       <c r="G60" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="H60" t="s">
         <v>15</v>
@@ -4914,21 +4943,21 @@
         <v>15</v>
       </c>
       <c r="L60" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
     </row>
     <row r="61" ht="30" spans="1:12">
       <c r="A61" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="B61" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C61" t="s">
         <v>14</v>
       </c>
       <c r="D61" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E61" t="s">
         <v>15</v>
@@ -4937,7 +4966,7 @@
         <v>15</v>
       </c>
       <c r="G61" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="H61" t="s">
         <v>15</v>
@@ -4952,12 +4981,12 @@
         <v>15</v>
       </c>
       <c r="L61" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
     </row>
     <row r="62" ht="30" spans="1:12">
       <c r="A62" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="B62" t="s">
         <v>13</v>
@@ -4966,7 +4995,7 @@
         <v>14</v>
       </c>
       <c r="D62" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E62" t="s">
         <v>15</v>
@@ -4975,7 +5004,7 @@
         <v>15</v>
       </c>
       <c r="G62" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="H62" t="s">
         <v>15</v>
@@ -4987,15 +5016,15 @@
         <v>15</v>
       </c>
       <c r="K62" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="L62" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
     </row>
     <row r="63" ht="54" spans="1:12">
       <c r="A63" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="B63" t="s">
         <v>13</v>
@@ -5013,7 +5042,7 @@
         <v>15</v>
       </c>
       <c r="G63" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="H63" t="s">
         <v>15</v>
@@ -5028,12 +5057,12 @@
         <v>15</v>
       </c>
       <c r="L63" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
     </row>
     <row r="64" ht="54" spans="1:12">
       <c r="A64" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="B64" t="s">
         <v>13</v>
@@ -5051,7 +5080,7 @@
         <v>15</v>
       </c>
       <c r="G64" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="H64" t="s">
         <v>15</v>
@@ -5062,16 +5091,16 @@
       <c r="J64" t="s">
         <v>15</v>
       </c>
-      <c r="K64" s="2" t="s">
-        <v>213</v>
+      <c r="K64" s="3" t="s">
+        <v>218</v>
       </c>
       <c r="L64" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
     </row>
     <row r="65" spans="1:12">
       <c r="A65" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="B65" t="s">
         <v>13</v>
@@ -5104,12 +5133,12 @@
         <v>15</v>
       </c>
       <c r="L65" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="66" ht="28.5" spans="1:12">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="66" ht="45" spans="1:12">
       <c r="A66" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="B66" t="s">
         <v>13</v>
@@ -5127,13 +5156,13 @@
         <v>15</v>
       </c>
       <c r="G66" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="H66" t="s">
         <v>15</v>
       </c>
       <c r="I66" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="J66" t="s">
         <v>15</v>
@@ -5142,12 +5171,12 @@
         <v>15</v>
       </c>
       <c r="L66" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
     </row>
     <row r="67" ht="42" spans="1:12">
       <c r="A67" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="B67" t="s">
         <v>13</v>
@@ -5165,7 +5194,7 @@
         <v>15</v>
       </c>
       <c r="G67" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="H67" t="s">
         <v>15</v>
@@ -5180,12 +5209,12 @@
         <v>15</v>
       </c>
       <c r="L67" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="68" ht="28.5" spans="1:12">
       <c r="A68" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="B68" t="s">
         <v>13</v>
@@ -5203,7 +5232,7 @@
         <v>15</v>
       </c>
       <c r="G68" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="H68" t="s">
         <v>15</v>
@@ -5218,12 +5247,12 @@
         <v>15</v>
       </c>
       <c r="L68" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="69" ht="40.5" spans="1:12">
       <c r="A69" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="B69" t="s">
         <v>13</v>
@@ -5241,7 +5270,7 @@
         <v>15</v>
       </c>
       <c r="G69" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="H69" t="s">
         <v>15</v>
@@ -5256,12 +5285,12 @@
         <v>15</v>
       </c>
       <c r="L69" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
     </row>
     <row r="70" ht="27" spans="1:12">
       <c r="A70" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="B70" t="s">
         <v>13</v>
@@ -5279,7 +5308,7 @@
         <v>15</v>
       </c>
       <c r="G70" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="H70" t="s">
         <v>15</v>
@@ -5294,15 +5323,15 @@
         <v>15</v>
       </c>
       <c r="L70" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="71" ht="27" spans="1:12">
       <c r="A71" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="B71" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C71" t="s">
         <v>14</v>
@@ -5317,7 +5346,7 @@
         <v>15</v>
       </c>
       <c r="G71" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="H71" t="s">
         <v>15</v>
@@ -5332,12 +5361,12 @@
         <v>15</v>
       </c>
       <c r="L71" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
     </row>
     <row r="72" ht="40.5" spans="1:12">
       <c r="A72" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="B72" t="s">
         <v>13</v>
@@ -5355,7 +5384,7 @@
         <v>15</v>
       </c>
       <c r="G72" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="H72" t="s">
         <v>15</v>
@@ -5370,12 +5399,12 @@
         <v>15</v>
       </c>
       <c r="L72" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="73" ht="67.5" spans="1:12">
       <c r="A73" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="B73" t="s">
         <v>13</v>
@@ -5393,7 +5422,7 @@
         <v>15</v>
       </c>
       <c r="G73" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="H73" t="s">
         <v>15</v>
@@ -5408,21 +5437,21 @@
         <v>15</v>
       </c>
       <c r="L73" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="74" spans="1:12">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="74" ht="30" spans="1:12">
       <c r="A74" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="B74" t="s">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="C74" t="s">
         <v>14</v>
       </c>
       <c r="D74" t="s">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="E74" t="s">
         <v>15</v>
@@ -5431,7 +5460,7 @@
         <v>15</v>
       </c>
       <c r="G74" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="H74" t="s">
         <v>15</v>
@@ -5443,24 +5472,24 @@
         <v>15</v>
       </c>
       <c r="K74" t="s">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="L74" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="75" ht="54" spans="1:12">
       <c r="A75" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="B75" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C75" t="s">
         <v>14</v>
       </c>
       <c r="D75" t="s">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="E75" t="s">
         <v>15</v>
@@ -5469,7 +5498,7 @@
         <v>15</v>
       </c>
       <c r="G75" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="H75" t="s">
         <v>15</v>
@@ -5481,24 +5510,24 @@
         <v>15</v>
       </c>
       <c r="K75" t="s">
-        <v>15</v>
+        <v>56</v>
       </c>
       <c r="L75" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
     </row>
     <row r="76" ht="30" spans="1:12">
       <c r="A76" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="B76" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C76" t="s">
         <v>14</v>
       </c>
       <c r="D76" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E76" t="s">
         <v>15</v>
@@ -5507,7 +5536,7 @@
         <v>15</v>
       </c>
       <c r="G76" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="H76" t="s">
         <v>15</v>
@@ -5519,24 +5548,24 @@
         <v>15</v>
       </c>
       <c r="K76" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="L76" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
     </row>
     <row r="77" ht="42" spans="1:12">
       <c r="A77" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="B77" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C77" t="s">
         <v>14</v>
       </c>
       <c r="D77" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E77" t="s">
         <v>15</v>
@@ -5545,7 +5574,7 @@
         <v>15</v>
       </c>
       <c r="G77" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="H77" t="s">
         <v>15</v>
@@ -5560,12 +5589,12 @@
         <v>15</v>
       </c>
       <c r="L77" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
     </row>
     <row r="78" ht="30" spans="1:12">
       <c r="A78" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="B78" t="s">
         <v>13</v>
@@ -5574,7 +5603,7 @@
         <v>14</v>
       </c>
       <c r="D78" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E78" t="s">
         <v>15</v>
@@ -5583,7 +5612,7 @@
         <v>15</v>
       </c>
       <c r="G78" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="H78" t="s">
         <v>15</v>
@@ -5595,15 +5624,15 @@
         <v>15</v>
       </c>
       <c r="K78" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="L78" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
     </row>
     <row r="79" ht="40.5" spans="1:12">
       <c r="A79" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="B79" t="s">
         <v>13</v>
@@ -5621,7 +5650,7 @@
         <v>15</v>
       </c>
       <c r="G79" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="H79" t="s">
         <v>15</v>
@@ -5636,12 +5665,12 @@
         <v>15</v>
       </c>
       <c r="L79" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="80" ht="30" spans="1:12">
       <c r="A80" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="B80" t="s">
         <v>13</v>
@@ -5659,7 +5688,7 @@
         <v>15</v>
       </c>
       <c r="G80" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="H80" t="s">
         <v>15</v>
@@ -5674,12 +5703,12 @@
         <v>15</v>
       </c>
       <c r="L80" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="81" ht="55.5" spans="1:12">
       <c r="A81" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="B81" t="s">
         <v>13</v>
@@ -5697,7 +5726,7 @@
         <v>15</v>
       </c>
       <c r="G81" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="H81" t="s">
         <v>15</v>
@@ -5712,12 +5741,12 @@
         <v>15</v>
       </c>
       <c r="L81" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="82" ht="28.5" spans="1:12">
       <c r="A82" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="B82" t="s">
         <v>13</v>
@@ -5735,7 +5764,7 @@
         <v>15</v>
       </c>
       <c r="G82" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="H82" t="s">
         <v>15</v>
@@ -5750,15 +5779,15 @@
         <v>15</v>
       </c>
       <c r="L82" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="83" spans="1:12">
       <c r="A83" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="B83" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C83" t="s">
         <v>14</v>
@@ -5773,7 +5802,7 @@
         <v>15</v>
       </c>
       <c r="G83" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="H83" t="s">
         <v>15</v>
@@ -5785,15 +5814,15 @@
         <v>15</v>
       </c>
       <c r="K83" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L83" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="84" ht="54" spans="1:12">
       <c r="A84" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="B84" t="s">
         <v>13</v>
@@ -5811,7 +5840,7 @@
         <v>15</v>
       </c>
       <c r="G84" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="H84" t="s">
         <v>15</v>
@@ -5826,12 +5855,12 @@
         <v>15</v>
       </c>
       <c r="L84" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="85" ht="54" spans="1:12">
       <c r="A85" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="B85" t="s">
         <v>13</v>
@@ -5849,7 +5878,7 @@
         <v>15</v>
       </c>
       <c r="G85" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="H85" t="s">
         <v>15</v>
@@ -5864,12 +5893,12 @@
         <v>15</v>
       </c>
       <c r="L85" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="86" ht="42" spans="1:12">
       <c r="A86" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="B86" t="s">
         <v>13</v>
@@ -5887,7 +5916,7 @@
         <v>15</v>
       </c>
       <c r="G86" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="H86" t="s">
         <v>15</v>
@@ -5902,21 +5931,21 @@
         <v>15</v>
       </c>
       <c r="L86" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
     </row>
     <row r="87" ht="30" spans="1:12">
       <c r="A87" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="B87" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C87" t="s">
         <v>14</v>
       </c>
       <c r="D87" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E87" t="s">
         <v>15</v>
@@ -5925,7 +5954,7 @@
         <v>15</v>
       </c>
       <c r="G87" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="H87" t="s">
         <v>15</v>
@@ -5937,15 +5966,15 @@
         <v>15</v>
       </c>
       <c r="K87" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="L87" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
     </row>
     <row r="88" ht="40.5" spans="1:12">
       <c r="A88" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="B88" t="s">
         <v>13</v>
@@ -5954,7 +5983,7 @@
         <v>14</v>
       </c>
       <c r="D88" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E88" t="s">
         <v>15</v>
@@ -5963,7 +5992,7 @@
         <v>15</v>
       </c>
       <c r="G88" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="H88" t="s">
         <v>15</v>
@@ -5978,21 +6007,21 @@
         <v>15</v>
       </c>
       <c r="L88" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
     </row>
     <row r="89" ht="30" spans="1:12">
       <c r="A89" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="B89" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C89" t="s">
         <v>14</v>
       </c>
       <c r="D89" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E89" t="s">
         <v>15</v>
@@ -6001,7 +6030,7 @@
         <v>15</v>
       </c>
       <c r="G89" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="H89" t="s">
         <v>15</v>
@@ -6016,12 +6045,12 @@
         <v>15</v>
       </c>
       <c r="L89" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
     </row>
     <row r="90" ht="54" spans="1:12">
       <c r="A90" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="B90" t="s">
         <v>13</v>
@@ -6030,7 +6059,7 @@
         <v>14</v>
       </c>
       <c r="D90" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E90" t="s">
         <v>15</v>
@@ -6039,27 +6068,24 @@
         <v>15</v>
       </c>
       <c r="G90" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="H90" t="s">
         <v>15</v>
       </c>
-      <c r="I90" t="s">
-        <v>15</v>
-      </c>
       <c r="J90" t="s">
         <v>15</v>
       </c>
       <c r="K90" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="L90" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="91" ht="54" spans="1:12">
-      <c r="A91" t="s">
-        <v>277</v>
+        <v>110</v>
+      </c>
+    </row>
+    <row r="91" ht="28.5" spans="1:12">
+      <c r="A91">
+        <v>92</v>
       </c>
       <c r="B91" t="s">
         <v>13</v>
@@ -6067,32 +6093,49 @@
       <c r="C91" t="s">
         <v>14</v>
       </c>
-      <c r="D91" t="s">
-        <v>15</v>
-      </c>
-      <c r="E91" t="s">
-        <v>15</v>
-      </c>
-      <c r="F91" t="s">
-        <v>15</v>
-      </c>
       <c r="G91" t="s">
-        <v>278</v>
-      </c>
-      <c r="H91" t="s">
-        <v>15</v>
+        <v>282</v>
       </c>
       <c r="I91" t="s">
-        <v>15</v>
-      </c>
-      <c r="J91" t="s">
-        <v>15</v>
-      </c>
-      <c r="K91" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="L91" t="s">
-        <v>280</v>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="92" ht="30" spans="1:12">
+      <c r="A92" t="s">
+        <v>283</v>
+      </c>
+      <c r="B92" t="s">
+        <v>13</v>
+      </c>
+      <c r="C92" t="s">
+        <v>14</v>
+      </c>
+      <c r="D92" t="s">
+        <v>15</v>
+      </c>
+      <c r="E92" t="s">
+        <v>15</v>
+      </c>
+      <c r="F92" t="s">
+        <v>15</v>
+      </c>
+      <c r="G92" t="s">
+        <v>284</v>
+      </c>
+      <c r="H92" t="s">
+        <v>15</v>
+      </c>
+      <c r="I92" t="s">
+        <v>15</v>
+      </c>
+      <c r="J92" t="s">
+        <v>15</v>
+      </c>
+      <c r="K92" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="L92" t="s">
+        <v>286</v>
       </c>
     </row>
   </sheetData>
@@ -6113,39 +6156,39 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
     </row>
     <row r="2" ht="45" spans="1:2">
       <c r="A2" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="B2" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="B3" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="B4" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="B5" t="s">
         <v>12</v>
@@ -6153,82 +6196,82 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" ht="27" spans="1:2">
       <c r="A7" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="B7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="B8" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
     </row>
     <row r="9" ht="27" spans="1:2">
       <c r="A9" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="B9" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="10" ht="75" spans="1:2">
       <c r="A10" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="B10" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
     </row>
     <row r="11" ht="75" spans="1:2">
       <c r="A11" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="B11" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
     </row>
     <row r="12" ht="57" spans="1:2">
       <c r="A12" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="B12" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:2">
       <c r="A13" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="B13" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
     </row>
     <row r="14" ht="60" spans="1:2">
       <c r="A14" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="B14" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
     </row>
     <row r="15" ht="75" spans="1:2">
       <c r="A15" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="B15" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
     </row>
   </sheetData>
@@ -6250,616 +6293,616 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
     </row>
     <row r="2" ht="73.5" spans="1:6">
       <c r="A2" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="B2" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="C2" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="D2" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="E2" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="F2" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
     </row>
     <row r="3" ht="103.5" spans="1:6">
       <c r="A3" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="B3" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="C3" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="D3" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="E3" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="F3" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
     </row>
     <row r="4" ht="45" spans="1:6">
       <c r="A4" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="B4" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="C4" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="D4" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="E4" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="F4" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
     </row>
     <row r="5" ht="45" spans="1:6">
       <c r="A5" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="B5" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="C5" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="D5" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="E5" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="F5" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
     </row>
     <row r="6" ht="45" spans="1:6">
       <c r="A6" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="B6" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="C6" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="D6" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="E6" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="F6" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
     </row>
     <row r="7" ht="75" spans="1:6">
       <c r="A7" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="B7" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="C7" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="D7" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="E7" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="F7" t="s">
-        <v>336</v>
+        <v>342</v>
       </c>
     </row>
     <row r="8" ht="45" spans="1:6">
       <c r="A8" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="B8" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="C8" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="D8" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="E8" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="F8" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
     </row>
     <row r="9" ht="45" spans="1:6">
       <c r="A9" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="B9" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="C9" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="D9" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="E9" t="s">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="F9" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
     </row>
     <row r="10" ht="58.5" spans="1:6">
       <c r="A10" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="B10" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="C10" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="D10" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="E10" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="F10" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
     </row>
     <row r="11" ht="60" spans="1:6">
       <c r="A11" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="B11" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="C11" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="D11" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="E11" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="F11" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
     </row>
     <row r="12" ht="58.5" spans="1:6">
       <c r="A12" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="B12" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="C12" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="D12" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="E12" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="F12" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:6">
       <c r="A13" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="B13" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="C13" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="D13" t="s">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="E13" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="F13" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
     </row>
     <row r="14" ht="58.5" spans="1:6">
       <c r="A14" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="B14" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="C14" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="D14" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="E14" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="F14" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
     </row>
     <row r="15" ht="58.5" spans="1:6">
       <c r="A15" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="B15" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="C15" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="D15" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="E15" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="F15" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
     </row>
     <row r="16" ht="58.5" spans="1:6">
       <c r="A16" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="B16" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="C16" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="D16" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="E16" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="F16" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
     </row>
     <row r="17" ht="58.5" spans="1:6">
       <c r="A17" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="B17" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="C17" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="D17" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="E17" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="F17" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
     </row>
     <row r="18" ht="58.5" spans="1:6">
       <c r="A18" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="B18" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="C18" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="D18" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="E18" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="F18" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
     </row>
     <row r="19" ht="58.5" spans="1:6">
       <c r="A19" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="B19" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="C19" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="D19" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="E19" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="F19" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
     </row>
     <row r="20" ht="72" spans="1:6">
       <c r="A20" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="B20" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="C20" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="D20" t="s">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="E20" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="F20" t="s">
-        <v>403</v>
+        <v>409</v>
       </c>
     </row>
     <row r="21" ht="58.5" spans="1:6">
       <c r="A21" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="B21" t="s">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="C21" t="s">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="D21" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="E21" t="s">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="F21" t="s">
-        <v>408</v>
+        <v>414</v>
       </c>
     </row>
     <row r="22" ht="58.5" spans="1:6">
       <c r="A22" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="B22" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="C22" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="D22" t="s">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="E22" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="F22" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
     </row>
     <row r="23" ht="58.5" spans="1:6">
       <c r="A23" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="B23" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="C23" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="D23" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="E23" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="F23" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
     </row>
     <row r="24" ht="58.5" spans="1:6">
       <c r="A24" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="B24" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="C24" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="D24" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="E24" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="F24" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
     </row>
     <row r="25" ht="90" spans="1:6">
       <c r="A25" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="B25" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C25" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="D25" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="E25" t="s">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="F25" t="s">
-        <v>428</v>
+        <v>434</v>
       </c>
     </row>
     <row r="26" ht="58.5" spans="1:6">
       <c r="A26" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="B26" t="s">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="C26" t="s">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="D26" t="s">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="E26" t="s">
-        <v>432</v>
+        <v>438</v>
       </c>
       <c r="F26" t="s">
-        <v>433</v>
+        <v>439</v>
       </c>
     </row>
     <row r="27" ht="58.5" spans="1:6">
       <c r="A27" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="B27" t="s">
-        <v>434</v>
+        <v>440</v>
       </c>
       <c r="C27" t="s">
-        <v>435</v>
+        <v>441</v>
       </c>
       <c r="D27" t="s">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="E27" t="s">
-        <v>437</v>
+        <v>443</v>
       </c>
       <c r="F27" t="s">
-        <v>438</v>
+        <v>444</v>
       </c>
     </row>
     <row r="28" ht="58.5" spans="1:6">
       <c r="A28" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="B28" t="s">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c r="C28" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="D28" t="s">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="E28" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="F28" t="s">
-        <v>442</v>
+        <v>448</v>
       </c>
     </row>
     <row r="29" ht="73.5" spans="1:6">
       <c r="A29" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="B29" t="s">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="C29" t="s">
-        <v>444</v>
+        <v>450</v>
       </c>
       <c r="D29" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="E29" t="s">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="F29" t="s">
-        <v>447</v>
+        <v>453</v>
       </c>
     </row>
     <row r="30" ht="58.5" spans="1:6">
       <c r="A30" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="B30" t="s">
-        <v>448</v>
+        <v>454</v>
       </c>
       <c r="C30" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D30" t="s">
-        <v>450</v>
+        <v>456</v>
       </c>
       <c r="E30" t="s">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="F30" t="s">
-        <v>452</v>
+        <v>458</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="B31" t="s">
-        <v>454</v>
+        <v>460</v>
       </c>
       <c r="C31" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="D31" t="s">
-        <v>456</v>
+        <v>462</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_david313-315(4).xlsx
+++ b/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_david313-315(4).xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="20385" windowHeight="10605"/>
   </bookViews>
   <sheets>
     <sheet name="圣诺汀之梦_大卫线313-315（下）" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1302" uniqueCount="463">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1301" uniqueCount="467">
   <si>
     <t>ID</t>
   </si>
@@ -99,7 +99,46 @@
     <t>2</t>
   </si>
   <si>
-    <t>choice(深入探究|jump(5))&amp;choice(视为陷阱|jump(66))</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>choice(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>深入探究</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>|jump(5))&amp;choice(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>视为陷阱</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>|jump(66))</t>
+    </r>
   </si>
   <si>
     <t>源类型=type:selectBC; 层级=1</t>
@@ -120,7 +159,97 @@
     <t>16 enhanced_suspence</t>
   </si>
   <si>
-    <t>源类型=type:txt_pb; 层级=3; 选项/备注=保持怀疑，或许能从中找到真相</t>
+    <t>unlockmusic(Music16)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>源类型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">=type:txt_pb; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>层级</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">=3; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>选项</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>备注</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>保持怀疑，或许能从中找到真相</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>;tag=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>深入探究</t>
+    </r>
   </si>
   <si>
     <t>6</t>
@@ -303,6 +432,9 @@
     <t>17 enhanced_suspense-tense-background-music</t>
   </si>
   <si>
+    <t>unlockmusic(Music17)</t>
+  </si>
+  <si>
     <t>源类型=type:txt_pb; 层级=21</t>
   </si>
   <si>
@@ -312,6 +444,9 @@
     <t>但上面的名字却并非你所想象的伊丽莎白，而是“亚当.格莱特”。</t>
   </si>
   <si>
+    <t>unlockscene(scene5)</t>
+  </si>
+  <si>
     <t>源类型=type:txt_pb; 层级=22</t>
   </si>
   <si>
@@ -589,6 +724,9 @@
   </si>
   <si>
     <t>3 enhanced leberch-horror-night</t>
+  </si>
+  <si>
+    <t>bgfade(sntzm_david313-315(4)_1,1)&amp;unlockmusic(Music3)</t>
   </si>
   <si>
     <t>源类型=type:txt_pb; 层级=51</t>
@@ -728,7 +866,94 @@
     <t>你放下手中那盘令人不安的磁带，尝试将一切扰乱你思绪的物品都赶出自己的视野。</t>
   </si>
   <si>
-    <t>源类型=type:txt_pb; 层级=3; 选项/备注=不为所动，以免陷入对方的节奏</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>源类型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">=type:txt_pb; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>层级</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">=3; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>选项</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>备注</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>不为所动，以免陷入对方的节奏</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>;tag=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>视为陷阱</t>
+    </r>
   </si>
   <si>
     <t>67</t>
@@ -2134,10 +2359,10 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2790,7 +3015,7 @@
       <c r="J3" t="s">
         <v>15</v>
       </c>
-      <c r="K3" t="s">
+      <c r="K3" s="2" t="s">
         <v>21</v>
       </c>
       <c r="L3" t="s">
@@ -2864,15 +3089,15 @@
         <v>15</v>
       </c>
       <c r="K5" t="s">
-        <v>15</v>
-      </c>
-      <c r="L5" t="s">
         <v>28</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="6" ht="54" spans="1:12">
       <c r="A6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B6" t="s">
         <v>13</v>
@@ -2890,7 +3115,7 @@
         <v>15</v>
       </c>
       <c r="G6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H6" t="s">
         <v>15</v>
@@ -2905,12 +3130,12 @@
         <v>15</v>
       </c>
       <c r="L6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" ht="40.5" spans="1:12">
       <c r="A7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B7" t="s">
         <v>13</v>
@@ -2928,7 +3153,7 @@
         <v>15</v>
       </c>
       <c r="G7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H7" t="s">
         <v>15</v>
@@ -2943,15 +3168,15 @@
         <v>15</v>
       </c>
       <c r="L7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" ht="27" spans="1:12">
       <c r="A8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C8" t="s">
         <v>14</v>
@@ -2966,7 +3191,7 @@
         <v>15</v>
       </c>
       <c r="G8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H8" t="s">
         <v>15</v>
@@ -2981,12 +3206,12 @@
         <v>15</v>
       </c>
       <c r="L8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" ht="27" spans="1:12">
       <c r="A9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B9" t="s">
         <v>13</v>
@@ -3001,7 +3226,7 @@
         <v>15</v>
       </c>
       <c r="G9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H9" t="s">
         <v>15</v>
@@ -3013,21 +3238,21 @@
         <v>15</v>
       </c>
       <c r="L9" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" ht="30" spans="1:12">
       <c r="A10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B10" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C10" t="s">
         <v>14</v>
       </c>
       <c r="D10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E10" t="s">
         <v>15</v>
@@ -3036,7 +3261,7 @@
         <v>15</v>
       </c>
       <c r="G10" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H10" t="s">
         <v>15</v>
@@ -3048,15 +3273,15 @@
         <v>15</v>
       </c>
       <c r="K10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11" ht="30" spans="1:12">
       <c r="A11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B11" t="s">
         <v>13</v>
@@ -3065,7 +3290,7 @@
         <v>14</v>
       </c>
       <c r="D11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E11" t="s">
         <v>15</v>
@@ -3074,7 +3299,7 @@
         <v>15</v>
       </c>
       <c r="G11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H11" t="s">
         <v>15</v>
@@ -3089,21 +3314,21 @@
         <v>15</v>
       </c>
       <c r="L11" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12" ht="55.5" spans="1:12">
       <c r="A12" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B12" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C12" t="s">
         <v>14</v>
       </c>
       <c r="D12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E12" t="s">
         <v>15</v>
@@ -3112,7 +3337,7 @@
         <v>15</v>
       </c>
       <c r="G12" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H12" t="s">
         <v>15</v>
@@ -3127,12 +3352,12 @@
         <v>15</v>
       </c>
       <c r="L12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13" ht="57" spans="1:12">
       <c r="A13" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B13" t="s">
         <v>13</v>
@@ -3141,7 +3366,7 @@
         <v>14</v>
       </c>
       <c r="D13" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E13" t="s">
         <v>15</v>
@@ -3150,7 +3375,7 @@
         <v>15</v>
       </c>
       <c r="G13" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H13" t="s">
         <v>15</v>
@@ -3162,15 +3387,15 @@
         <v>15</v>
       </c>
       <c r="K13" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="14" ht="42" spans="1:12">
       <c r="A14" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B14" t="s">
         <v>13</v>
@@ -3188,7 +3413,7 @@
         <v>15</v>
       </c>
       <c r="G14" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H14" t="s">
         <v>15</v>
@@ -3203,15 +3428,15 @@
         <v>15</v>
       </c>
       <c r="L14" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15" ht="40.5" spans="1:12">
       <c r="A15" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B15" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C15" t="s">
         <v>14</v>
@@ -3226,7 +3451,7 @@
         <v>15</v>
       </c>
       <c r="G15" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H15" t="s">
         <v>15</v>
@@ -3241,12 +3466,12 @@
         <v>15</v>
       </c>
       <c r="L15" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="16" spans="1:12">
       <c r="A16" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B16" t="s">
         <v>13</v>
@@ -3264,7 +3489,7 @@
         <v>15</v>
       </c>
       <c r="G16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H16" t="s">
         <v>15</v>
@@ -3279,15 +3504,15 @@
         <v>15</v>
       </c>
       <c r="L16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17" spans="1:12">
       <c r="A17" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C17" t="s">
         <v>14</v>
@@ -3302,7 +3527,7 @@
         <v>15</v>
       </c>
       <c r="G17" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H17" t="s">
         <v>15</v>
@@ -3317,12 +3542,12 @@
         <v>15</v>
       </c>
       <c r="L17" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="18" ht="40.5" spans="1:12">
       <c r="A18" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B18" t="s">
         <v>13</v>
@@ -3340,7 +3565,7 @@
         <v>15</v>
       </c>
       <c r="G18" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H18" t="s">
         <v>15</v>
@@ -3355,12 +3580,12 @@
         <v>15</v>
       </c>
       <c r="L18" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="19" ht="54" spans="1:12">
       <c r="A19" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B19" t="s">
         <v>13</v>
@@ -3378,7 +3603,7 @@
         <v>15</v>
       </c>
       <c r="G19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H19" t="s">
         <v>15</v>
@@ -3390,15 +3615,15 @@
         <v>15</v>
       </c>
       <c r="K19" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="L19" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="20" ht="40.5" spans="1:12">
       <c r="A20" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B20" t="s">
         <v>13</v>
@@ -3416,7 +3641,7 @@
         <v>15</v>
       </c>
       <c r="G20" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H20" t="s">
         <v>15</v>
@@ -3431,12 +3656,12 @@
         <v>15</v>
       </c>
       <c r="L20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="21" ht="57" spans="1:12">
       <c r="A21" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B21" t="s">
         <v>13</v>
@@ -3454,7 +3679,7 @@
         <v>15</v>
       </c>
       <c r="G21" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H21" t="s">
         <v>15</v>
@@ -3466,15 +3691,15 @@
         <v>15</v>
       </c>
       <c r="L21" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="22" spans="1:12">
       <c r="A22" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B22" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C22" t="s">
         <v>14</v>
@@ -3489,7 +3714,7 @@
         <v>15</v>
       </c>
       <c r="G22" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H22" t="s">
         <v>15</v>
@@ -3504,12 +3729,12 @@
         <v>15</v>
       </c>
       <c r="L22" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="23" ht="67.5" spans="1:12">
       <c r="A23" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B23" t="s">
         <v>13</v>
@@ -3527,27 +3752,27 @@
         <v>15</v>
       </c>
       <c r="G23" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H23" t="s">
         <v>15</v>
       </c>
       <c r="I23" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J23" t="s">
         <v>15</v>
       </c>
       <c r="K23" t="s">
-        <v>15</v>
+        <v>90</v>
       </c>
       <c r="L23" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="24" ht="30" spans="1:12">
       <c r="A24" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B24" t="s">
         <v>13</v>
@@ -3565,7 +3790,7 @@
         <v>15</v>
       </c>
       <c r="G24" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H24" t="s">
         <v>15</v>
@@ -3577,15 +3802,15 @@
         <v>15</v>
       </c>
       <c r="K24" t="s">
-        <v>15</v>
+        <v>94</v>
       </c>
       <c r="L24" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="25" spans="1:12">
       <c r="A25" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B25" t="s">
         <v>13</v>
@@ -3603,10 +3828,10 @@
         <v>15</v>
       </c>
       <c r="G25" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="H25" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="I25" t="s">
         <v>15</v>
@@ -3615,15 +3840,15 @@
         <v>15</v>
       </c>
       <c r="K25" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="L25" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="26" ht="54" spans="1:12">
       <c r="A26" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B26" t="s">
         <v>13</v>
@@ -3641,7 +3866,7 @@
         <v>15</v>
       </c>
       <c r="G26" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="H26" t="s">
         <v>15</v>
@@ -3656,12 +3881,12 @@
         <v>15</v>
       </c>
       <c r="L26" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="27" ht="69" spans="1:12">
       <c r="A27" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B27" t="s">
         <v>13</v>
@@ -3679,7 +3904,7 @@
         <v>15</v>
       </c>
       <c r="G27" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="H27" t="s">
         <v>15</v>
@@ -3691,15 +3916,15 @@
         <v>15</v>
       </c>
       <c r="K27" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="L27" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
     </row>
     <row r="28" ht="40.5" spans="1:12">
       <c r="A28" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B28" t="s">
         <v>13</v>
@@ -3717,7 +3942,7 @@
         <v>15</v>
       </c>
       <c r="G28" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="H28" t="s">
         <v>15</v>
@@ -3732,12 +3957,12 @@
         <v>15</v>
       </c>
       <c r="L28" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
     </row>
     <row r="29" ht="67.5" spans="1:12">
       <c r="A29" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B29" t="s">
         <v>13</v>
@@ -3755,7 +3980,7 @@
         <v>15</v>
       </c>
       <c r="G29" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="H29" t="s">
         <v>15</v>
@@ -3770,12 +3995,12 @@
         <v>15</v>
       </c>
       <c r="L29" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="30" ht="28.5" spans="1:12">
       <c r="A30" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B30" t="s">
         <v>13</v>
@@ -3793,7 +4018,7 @@
         <v>15</v>
       </c>
       <c r="G30" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="H30" t="s">
         <v>15</v>
@@ -3808,12 +4033,12 @@
         <v>15</v>
       </c>
       <c r="L30" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
     <row r="31" ht="54" spans="1:12">
       <c r="A31" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B31" t="s">
         <v>13</v>
@@ -3831,7 +4056,7 @@
         <v>15</v>
       </c>
       <c r="G31" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="H31" t="s">
         <v>15</v>
@@ -3846,12 +4071,12 @@
         <v>15</v>
       </c>
       <c r="L31" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="32" ht="42" spans="1:12">
       <c r="A32" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B32" t="s">
         <v>13</v>
@@ -3869,7 +4094,7 @@
         <v>15</v>
       </c>
       <c r="G32" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="H32" t="s">
         <v>15</v>
@@ -3884,12 +4109,12 @@
         <v>15</v>
       </c>
       <c r="L32" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="33" spans="1:12">
       <c r="A33" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="B33" t="s">
         <v>13</v>
@@ -3907,7 +4132,7 @@
         <v>15</v>
       </c>
       <c r="G33" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="H33" t="s">
         <v>15</v>
@@ -3919,15 +4144,15 @@
         <v>15</v>
       </c>
       <c r="K33" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="L33" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="34" ht="40.5" spans="1:12">
       <c r="A34" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B34" t="s">
         <v>13</v>
@@ -3945,7 +4170,7 @@
         <v>15</v>
       </c>
       <c r="G34" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="H34" t="s">
         <v>15</v>
@@ -3960,12 +4185,12 @@
         <v>15</v>
       </c>
       <c r="L34" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="35" ht="40.5" spans="1:12">
       <c r="A35" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B35" t="s">
         <v>13</v>
@@ -3983,7 +4208,7 @@
         <v>15</v>
       </c>
       <c r="G35" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="H35" t="s">
         <v>15</v>
@@ -3998,12 +4223,12 @@
         <v>15</v>
       </c>
       <c r="L35" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="36" spans="1:12">
       <c r="A36" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B36" t="s">
         <v>13</v>
@@ -4021,7 +4246,7 @@
         <v>15</v>
       </c>
       <c r="G36" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="H36" t="s">
         <v>15</v>
@@ -4036,12 +4261,12 @@
         <v>15</v>
       </c>
       <c r="L36" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
     </row>
     <row r="37" ht="27" spans="1:12">
       <c r="A37" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="B37" t="s">
         <v>13</v>
@@ -4059,7 +4284,7 @@
         <v>15</v>
       </c>
       <c r="G37" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="H37" t="s">
         <v>15</v>
@@ -4074,12 +4299,12 @@
         <v>15</v>
       </c>
       <c r="L37" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="38" ht="60" spans="1:12">
       <c r="A38" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="B38" t="s">
         <v>13</v>
@@ -4097,7 +4322,7 @@
         <v>15</v>
       </c>
       <c r="G38" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="H38" t="s">
         <v>15</v>
@@ -4112,12 +4337,12 @@
         <v>15</v>
       </c>
       <c r="L38" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="39" ht="40.5" spans="1:12">
       <c r="A39" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B39" t="s">
         <v>13</v>
@@ -4135,7 +4360,7 @@
         <v>15</v>
       </c>
       <c r="G39" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="H39" t="s">
         <v>15</v>
@@ -4150,12 +4375,12 @@
         <v>15</v>
       </c>
       <c r="L39" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="40" ht="27" spans="1:12">
       <c r="A40" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="B40" t="s">
         <v>13</v>
@@ -4173,7 +4398,7 @@
         <v>15</v>
       </c>
       <c r="G40" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="H40" t="s">
         <v>15</v>
@@ -4188,12 +4413,12 @@
         <v>15</v>
       </c>
       <c r="L40" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
     </row>
     <row r="41" ht="43.5" spans="1:12">
       <c r="A41" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="B41" t="s">
         <v>13</v>
@@ -4211,7 +4436,7 @@
         <v>15</v>
       </c>
       <c r="G41" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="H41" t="s">
         <v>15</v>
@@ -4226,12 +4451,12 @@
         <v>15</v>
       </c>
       <c r="L41" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
     </row>
     <row r="42" ht="27" spans="1:12">
       <c r="A42" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="B42" t="s">
         <v>13</v>
@@ -4249,7 +4474,7 @@
         <v>15</v>
       </c>
       <c r="G42" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="H42" t="s">
         <v>15</v>
@@ -4264,12 +4489,12 @@
         <v>15</v>
       </c>
       <c r="L42" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="43" ht="30" spans="1:12">
       <c r="A43" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B43" t="s">
         <v>13</v>
@@ -4287,7 +4512,7 @@
         <v>15</v>
       </c>
       <c r="G43" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="H43" t="s">
         <v>15</v>
@@ -4302,12 +4527,12 @@
         <v>15</v>
       </c>
       <c r="L43" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
     </row>
     <row r="44" ht="27" spans="1:12">
       <c r="A44" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="B44" t="s">
         <v>13</v>
@@ -4325,7 +4550,7 @@
         <v>15</v>
       </c>
       <c r="G44" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="H44" t="s">
         <v>15</v>
@@ -4340,12 +4565,12 @@
         <v>15</v>
       </c>
       <c r="L44" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
     </row>
     <row r="45" ht="57" spans="1:12">
       <c r="A45" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B45" t="s">
         <v>13</v>
@@ -4363,7 +4588,7 @@
         <v>15</v>
       </c>
       <c r="G45" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="H45" t="s">
         <v>15</v>
@@ -4378,12 +4603,12 @@
         <v>15</v>
       </c>
       <c r="L45" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
     </row>
     <row r="46" ht="54" spans="1:12">
       <c r="A46" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="B46" t="s">
         <v>13</v>
@@ -4401,7 +4626,7 @@
         <v>15</v>
       </c>
       <c r="G46" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="H46" t="s">
         <v>15</v>
@@ -4416,12 +4641,12 @@
         <v>15</v>
       </c>
       <c r="L46" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
     </row>
     <row r="47" ht="40.5" spans="1:12">
       <c r="A47" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="B47" t="s">
         <v>13</v>
@@ -4439,7 +4664,7 @@
         <v>15</v>
       </c>
       <c r="G47" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="H47" t="s">
         <v>15</v>
@@ -4454,12 +4679,12 @@
         <v>15</v>
       </c>
       <c r="L47" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
     </row>
     <row r="48" ht="54" spans="1:12">
       <c r="A48" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B48" t="s">
         <v>13</v>
@@ -4477,7 +4702,7 @@
         <v>15</v>
       </c>
       <c r="G48" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="H48" t="s">
         <v>15</v>
@@ -4489,15 +4714,15 @@
         <v>15</v>
       </c>
       <c r="K48" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="L48" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
     </row>
     <row r="49" spans="1:12">
       <c r="A49" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="B49" t="s">
         <v>13</v>
@@ -4515,7 +4740,7 @@
         <v>15</v>
       </c>
       <c r="G49" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="H49" t="s">
         <v>15</v>
@@ -4530,12 +4755,12 @@
         <v>15</v>
       </c>
       <c r="L49" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="50" ht="40.5" spans="1:12">
       <c r="A50" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="B50" t="s">
         <v>13</v>
@@ -4552,8 +4777,8 @@
       <c r="F50" t="s">
         <v>15</v>
       </c>
-      <c r="G50" s="2" t="s">
-        <v>174</v>
+      <c r="G50" s="3" t="s">
+        <v>177</v>
       </c>
       <c r="H50" t="s">
         <v>15</v>
@@ -4568,12 +4793,12 @@
         <v>15</v>
       </c>
       <c r="L50" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
     </row>
     <row r="51" ht="40.5" spans="1:12">
       <c r="A51" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B51" t="s">
         <v>13</v>
@@ -4591,7 +4816,7 @@
         <v>15</v>
       </c>
       <c r="G51" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="H51" t="s">
         <v>15</v>
@@ -4606,12 +4831,12 @@
         <v>15</v>
       </c>
       <c r="L51" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
     </row>
     <row r="52" ht="67.5" spans="1:12">
       <c r="A52" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B52" t="s">
         <v>13</v>
@@ -4629,12 +4854,11 @@
         <v>15</v>
       </c>
       <c r="G52" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="H52" t="s">
         <v>15</v>
       </c>
-      <c r="I52"/>
       <c r="J52" t="s">
         <v>15</v>
       </c>
@@ -4642,12 +4866,12 @@
         <v>15</v>
       </c>
       <c r="L52" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
     <row r="53" ht="45" spans="1:12">
       <c r="A53" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B53" t="s">
         <v>13</v>
@@ -4665,27 +4889,27 @@
         <v>15</v>
       </c>
       <c r="G53" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="H53" t="s">
         <v>15</v>
       </c>
       <c r="I53" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="J53" t="s">
         <v>15</v>
       </c>
       <c r="K53" t="s">
-        <v>18</v>
+        <v>188</v>
       </c>
       <c r="L53" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="54" ht="67.5" spans="1:12">
       <c r="A54" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B54" t="s">
         <v>13</v>
@@ -4703,7 +4927,7 @@
         <v>15</v>
       </c>
       <c r="G54" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="H54" t="s">
         <v>15</v>
@@ -4718,12 +4942,12 @@
         <v>15</v>
       </c>
       <c r="L54" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
     </row>
     <row r="55" ht="40.5" spans="1:12">
       <c r="A55" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="B55" t="s">
         <v>13</v>
@@ -4741,7 +4965,7 @@
         <v>15</v>
       </c>
       <c r="G55" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="H55" t="s">
         <v>15</v>
@@ -4752,19 +4976,16 @@
       <c r="J55" t="s">
         <v>15</v>
       </c>
-      <c r="K55" t="s">
-        <v>15</v>
-      </c>
       <c r="L55" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
     </row>
     <row r="56" spans="1:12">
       <c r="A56" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="B56" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C56" t="s">
         <v>14</v>
@@ -4779,7 +5000,7 @@
         <v>15</v>
       </c>
       <c r="G56" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="H56" t="s">
         <v>15</v>
@@ -4794,21 +5015,21 @@
         <v>15</v>
       </c>
       <c r="L56" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
     </row>
     <row r="57" ht="30" spans="1:12">
       <c r="A57" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="B57" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C57" t="s">
         <v>14</v>
       </c>
       <c r="D57" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E57" t="s">
         <v>15</v>
@@ -4817,7 +5038,7 @@
         <v>15</v>
       </c>
       <c r="G57" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="H57" t="s">
         <v>15</v>
@@ -4829,15 +5050,15 @@
         <v>15</v>
       </c>
       <c r="K57" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L57" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
     </row>
     <row r="58" ht="69" spans="1:12">
       <c r="A58" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="B58" t="s">
         <v>13</v>
@@ -4846,7 +5067,7 @@
         <v>14</v>
       </c>
       <c r="D58" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E58" t="s">
         <v>15</v>
@@ -4855,7 +5076,7 @@
         <v>15</v>
       </c>
       <c r="G58" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="H58" t="s">
         <v>15</v>
@@ -4870,21 +5091,21 @@
         <v>15</v>
       </c>
       <c r="L58" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
     </row>
     <row r="59" ht="30" spans="1:12">
       <c r="A59" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="B59" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C59" t="s">
         <v>14</v>
       </c>
       <c r="D59" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E59" t="s">
         <v>15</v>
@@ -4893,7 +5114,7 @@
         <v>15</v>
       </c>
       <c r="G59" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="H59" t="s">
         <v>15</v>
@@ -4908,12 +5129,12 @@
         <v>15</v>
       </c>
       <c r="L59" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
     </row>
     <row r="60" ht="67.5" spans="1:12">
       <c r="A60" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="B60" t="s">
         <v>13</v>
@@ -4922,7 +5143,7 @@
         <v>14</v>
       </c>
       <c r="D60" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E60" t="s">
         <v>15</v>
@@ -4931,7 +5152,7 @@
         <v>15</v>
       </c>
       <c r="G60" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="H60" t="s">
         <v>15</v>
@@ -4943,21 +5164,21 @@
         <v>15</v>
       </c>
       <c r="L60" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
     </row>
     <row r="61" ht="30" spans="1:12">
       <c r="A61" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="B61" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C61" t="s">
         <v>14</v>
       </c>
       <c r="D61" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E61" t="s">
         <v>15</v>
@@ -4966,7 +5187,7 @@
         <v>15</v>
       </c>
       <c r="G61" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="H61" t="s">
         <v>15</v>
@@ -4981,12 +5202,12 @@
         <v>15</v>
       </c>
       <c r="L61" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
     </row>
     <row r="62" ht="30" spans="1:12">
       <c r="A62" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="B62" t="s">
         <v>13</v>
@@ -4995,7 +5216,7 @@
         <v>14</v>
       </c>
       <c r="D62" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E62" t="s">
         <v>15</v>
@@ -5004,7 +5225,7 @@
         <v>15</v>
       </c>
       <c r="G62" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="H62" t="s">
         <v>15</v>
@@ -5016,15 +5237,15 @@
         <v>15</v>
       </c>
       <c r="K62" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L62" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
     </row>
     <row r="63" ht="54" spans="1:12">
       <c r="A63" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="B63" t="s">
         <v>13</v>
@@ -5042,7 +5263,7 @@
         <v>15</v>
       </c>
       <c r="G63" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="H63" t="s">
         <v>15</v>
@@ -5057,12 +5278,12 @@
         <v>15</v>
       </c>
       <c r="L63" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
     </row>
     <row r="64" ht="54" spans="1:12">
       <c r="A64" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="B64" t="s">
         <v>13</v>
@@ -5080,7 +5301,7 @@
         <v>15</v>
       </c>
       <c r="G64" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="H64" t="s">
         <v>15</v>
@@ -5091,16 +5312,16 @@
       <c r="J64" t="s">
         <v>15</v>
       </c>
-      <c r="K64" s="3" t="s">
-        <v>218</v>
+      <c r="K64" s="2" t="s">
+        <v>222</v>
       </c>
       <c r="L64" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
     </row>
     <row r="65" spans="1:12">
       <c r="A65" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="B65" t="s">
         <v>13</v>
@@ -5138,7 +5359,7 @@
     </row>
     <row r="66" ht="45" spans="1:12">
       <c r="A66" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="B66" t="s">
         <v>13</v>
@@ -5156,7 +5377,7 @@
         <v>15</v>
       </c>
       <c r="G66" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="H66" t="s">
         <v>15</v>
@@ -5168,15 +5389,15 @@
         <v>15</v>
       </c>
       <c r="K66" t="s">
-        <v>15</v>
-      </c>
-      <c r="L66" t="s">
-        <v>223</v>
+        <v>28</v>
+      </c>
+      <c r="L66" s="3" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="67" ht="42" spans="1:12">
       <c r="A67" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="B67" t="s">
         <v>13</v>
@@ -5194,7 +5415,7 @@
         <v>15</v>
       </c>
       <c r="G67" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="H67" t="s">
         <v>15</v>
@@ -5209,12 +5430,12 @@
         <v>15</v>
       </c>
       <c r="L67" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="68" ht="28.5" spans="1:12">
       <c r="A68" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="B68" t="s">
         <v>13</v>
@@ -5232,7 +5453,7 @@
         <v>15</v>
       </c>
       <c r="G68" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="H68" t="s">
         <v>15</v>
@@ -5247,12 +5468,12 @@
         <v>15</v>
       </c>
       <c r="L68" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="69" ht="40.5" spans="1:12">
       <c r="A69" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="B69" t="s">
         <v>13</v>
@@ -5270,7 +5491,7 @@
         <v>15</v>
       </c>
       <c r="G69" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="H69" t="s">
         <v>15</v>
@@ -5285,12 +5506,12 @@
         <v>15</v>
       </c>
       <c r="L69" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
     </row>
     <row r="70" ht="27" spans="1:12">
       <c r="A70" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="B70" t="s">
         <v>13</v>
@@ -5308,7 +5529,7 @@
         <v>15</v>
       </c>
       <c r="G70" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="H70" t="s">
         <v>15</v>
@@ -5323,15 +5544,15 @@
         <v>15</v>
       </c>
       <c r="L70" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="71" ht="27" spans="1:12">
       <c r="A71" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="B71" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C71" t="s">
         <v>14</v>
@@ -5346,7 +5567,7 @@
         <v>15</v>
       </c>
       <c r="G71" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="H71" t="s">
         <v>15</v>
@@ -5361,12 +5582,12 @@
         <v>15</v>
       </c>
       <c r="L71" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
     </row>
     <row r="72" ht="40.5" spans="1:12">
       <c r="A72" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="B72" t="s">
         <v>13</v>
@@ -5384,7 +5605,7 @@
         <v>15</v>
       </c>
       <c r="G72" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="H72" t="s">
         <v>15</v>
@@ -5399,12 +5620,12 @@
         <v>15</v>
       </c>
       <c r="L72" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="73" ht="67.5" spans="1:12">
       <c r="A73" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="B73" t="s">
         <v>13</v>
@@ -5422,7 +5643,7 @@
         <v>15</v>
       </c>
       <c r="G73" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="H73" t="s">
         <v>15</v>
@@ -5437,21 +5658,21 @@
         <v>15</v>
       </c>
       <c r="L73" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
     </row>
     <row r="74" ht="30" spans="1:12">
       <c r="A74" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="B74" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C74" t="s">
         <v>14</v>
       </c>
       <c r="D74" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E74" t="s">
         <v>15</v>
@@ -5460,7 +5681,7 @@
         <v>15</v>
       </c>
       <c r="G74" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="H74" t="s">
         <v>15</v>
@@ -5472,24 +5693,24 @@
         <v>15</v>
       </c>
       <c r="K74" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L74" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="75" ht="54" spans="1:12">
       <c r="A75" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="B75" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C75" t="s">
         <v>14</v>
       </c>
       <c r="D75" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E75" t="s">
         <v>15</v>
@@ -5498,7 +5719,7 @@
         <v>15</v>
       </c>
       <c r="G75" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="H75" t="s">
         <v>15</v>
@@ -5510,24 +5731,24 @@
         <v>15</v>
       </c>
       <c r="K75" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L75" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
     </row>
     <row r="76" ht="30" spans="1:12">
       <c r="A76" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="B76" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C76" t="s">
         <v>14</v>
       </c>
       <c r="D76" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E76" t="s">
         <v>15</v>
@@ -5536,7 +5757,7 @@
         <v>15</v>
       </c>
       <c r="G76" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="H76" t="s">
         <v>15</v>
@@ -5548,24 +5769,24 @@
         <v>15</v>
       </c>
       <c r="K76" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L76" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
     </row>
     <row r="77" ht="42" spans="1:12">
       <c r="A77" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="B77" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C77" t="s">
         <v>14</v>
       </c>
       <c r="D77" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E77" t="s">
         <v>15</v>
@@ -5574,7 +5795,7 @@
         <v>15</v>
       </c>
       <c r="G77" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="H77" t="s">
         <v>15</v>
@@ -5589,12 +5810,12 @@
         <v>15</v>
       </c>
       <c r="L77" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
     </row>
     <row r="78" ht="30" spans="1:12">
       <c r="A78" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="B78" t="s">
         <v>13</v>
@@ -5603,7 +5824,7 @@
         <v>14</v>
       </c>
       <c r="D78" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E78" t="s">
         <v>15</v>
@@ -5612,7 +5833,7 @@
         <v>15</v>
       </c>
       <c r="G78" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="H78" t="s">
         <v>15</v>
@@ -5624,15 +5845,15 @@
         <v>15</v>
       </c>
       <c r="K78" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="L78" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
     </row>
     <row r="79" ht="40.5" spans="1:12">
       <c r="A79" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B79" t="s">
         <v>13</v>
@@ -5650,7 +5871,7 @@
         <v>15</v>
       </c>
       <c r="G79" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="H79" t="s">
         <v>15</v>
@@ -5665,12 +5886,12 @@
         <v>15</v>
       </c>
       <c r="L79" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="80" ht="30" spans="1:12">
       <c r="A80" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="B80" t="s">
         <v>13</v>
@@ -5688,7 +5909,7 @@
         <v>15</v>
       </c>
       <c r="G80" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="H80" t="s">
         <v>15</v>
@@ -5703,12 +5924,12 @@
         <v>15</v>
       </c>
       <c r="L80" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="81" ht="55.5" spans="1:12">
       <c r="A81" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="B81" t="s">
         <v>13</v>
@@ -5726,7 +5947,7 @@
         <v>15</v>
       </c>
       <c r="G81" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="H81" t="s">
         <v>15</v>
@@ -5741,12 +5962,12 @@
         <v>15</v>
       </c>
       <c r="L81" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="82" ht="28.5" spans="1:12">
       <c r="A82" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="B82" t="s">
         <v>13</v>
@@ -5764,7 +5985,7 @@
         <v>15</v>
       </c>
       <c r="G82" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="H82" t="s">
         <v>15</v>
@@ -5779,15 +6000,15 @@
         <v>15</v>
       </c>
       <c r="L82" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="83" spans="1:12">
       <c r="A83" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="B83" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C83" t="s">
         <v>14</v>
@@ -5802,7 +6023,7 @@
         <v>15</v>
       </c>
       <c r="G83" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="H83" t="s">
         <v>15</v>
@@ -5817,12 +6038,12 @@
         <v>18</v>
       </c>
       <c r="L83" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="84" ht="54" spans="1:12">
       <c r="A84" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="B84" t="s">
         <v>13</v>
@@ -5840,7 +6061,7 @@
         <v>15</v>
       </c>
       <c r="G84" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="H84" t="s">
         <v>15</v>
@@ -5855,12 +6076,12 @@
         <v>15</v>
       </c>
       <c r="L84" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="85" ht="54" spans="1:12">
       <c r="A85" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="B85" t="s">
         <v>13</v>
@@ -5878,7 +6099,7 @@
         <v>15</v>
       </c>
       <c r="G85" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="H85" t="s">
         <v>15</v>
@@ -5893,12 +6114,12 @@
         <v>15</v>
       </c>
       <c r="L85" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="86" ht="42" spans="1:12">
       <c r="A86" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="B86" t="s">
         <v>13</v>
@@ -5916,7 +6137,7 @@
         <v>15</v>
       </c>
       <c r="G86" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="H86" t="s">
         <v>15</v>
@@ -5931,21 +6152,21 @@
         <v>15</v>
       </c>
       <c r="L86" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="87" ht="30" spans="1:12">
       <c r="A87" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="B87" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C87" t="s">
         <v>14</v>
       </c>
       <c r="D87" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E87" t="s">
         <v>15</v>
@@ -5954,7 +6175,7 @@
         <v>15</v>
       </c>
       <c r="G87" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="H87" t="s">
         <v>15</v>
@@ -5966,15 +6187,15 @@
         <v>15</v>
       </c>
       <c r="K87" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L87" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
     </row>
     <row r="88" ht="40.5" spans="1:12">
       <c r="A88" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="B88" t="s">
         <v>13</v>
@@ -5983,7 +6204,7 @@
         <v>14</v>
       </c>
       <c r="D88" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E88" t="s">
         <v>15</v>
@@ -5992,7 +6213,7 @@
         <v>15</v>
       </c>
       <c r="G88" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="H88" t="s">
         <v>15</v>
@@ -6007,21 +6228,21 @@
         <v>15</v>
       </c>
       <c r="L88" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
     </row>
     <row r="89" ht="30" spans="1:12">
       <c r="A89" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="B89" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C89" t="s">
         <v>14</v>
       </c>
       <c r="D89" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E89" t="s">
         <v>15</v>
@@ -6030,7 +6251,7 @@
         <v>15</v>
       </c>
       <c r="G89" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="H89" t="s">
         <v>15</v>
@@ -6045,12 +6266,12 @@
         <v>15</v>
       </c>
       <c r="L89" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
     </row>
     <row r="90" ht="54" spans="1:12">
       <c r="A90" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="B90" t="s">
         <v>13</v>
@@ -6059,7 +6280,7 @@
         <v>14</v>
       </c>
       <c r="D90" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E90" t="s">
         <v>15</v>
@@ -6068,7 +6289,7 @@
         <v>15</v>
       </c>
       <c r="G90" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="H90" t="s">
         <v>15</v>
@@ -6077,10 +6298,10 @@
         <v>15</v>
       </c>
       <c r="K90" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L90" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="91" ht="28.5" spans="1:12">
@@ -6094,7 +6315,7 @@
         <v>14</v>
       </c>
       <c r="G91" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="I91" t="s">
         <v>16</v>
@@ -6102,7 +6323,7 @@
     </row>
     <row r="92" ht="30" spans="1:12">
       <c r="A92" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="B92" t="s">
         <v>13</v>
@@ -6120,7 +6341,7 @@
         <v>15</v>
       </c>
       <c r="G92" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="H92" t="s">
         <v>15</v>
@@ -6131,11 +6352,11 @@
       <c r="J92" t="s">
         <v>15</v>
       </c>
-      <c r="K92" s="3" t="s">
-        <v>285</v>
+      <c r="K92" s="2" t="s">
+        <v>289</v>
       </c>
       <c r="L92" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
     </row>
   </sheetData>
@@ -6156,39 +6377,39 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
     </row>
     <row r="2" ht="45" spans="1:2">
       <c r="A2" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="B2" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="B3" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="B4" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="B5" t="s">
         <v>12</v>
@@ -6196,7 +6417,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="B6" t="s">
         <v>20</v>
@@ -6204,7 +6425,7 @@
     </row>
     <row r="7" ht="27" spans="1:2">
       <c r="A7" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="B7" t="s">
         <v>20</v>
@@ -6212,66 +6433,66 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="B8" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
     </row>
     <row r="9" ht="27" spans="1:2">
       <c r="A9" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="B9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="10" ht="75" spans="1:2">
       <c r="A10" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="B10" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="11" ht="75" spans="1:2">
       <c r="A11" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="B11" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
     </row>
     <row r="12" ht="57" spans="1:2">
       <c r="A12" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="B12" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:2">
       <c r="A13" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="B13" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
     </row>
     <row r="14" ht="60" spans="1:2">
       <c r="A14" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="B14" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
     </row>
     <row r="15" ht="75" spans="1:2">
       <c r="A15" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="B15" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
     </row>
   </sheetData>
@@ -6293,616 +6514,616 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
     </row>
     <row r="2" ht="73.5" spans="1:6">
       <c r="A2" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="B2" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="C2" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="D2" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="E2" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="F2" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
     </row>
     <row r="3" ht="103.5" spans="1:6">
       <c r="A3" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="B3" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="C3" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="D3" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="E3" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="F3" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="4" ht="45" spans="1:6">
       <c r="A4" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="B4" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="C4" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="D4" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="E4" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="F4" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
     </row>
     <row r="5" ht="45" spans="1:6">
       <c r="A5" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="B5" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="C5" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="D5" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E5" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="F5" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
     </row>
     <row r="6" ht="45" spans="1:6">
       <c r="A6" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="B6" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="C6" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="D6" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="E6" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="F6" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
     </row>
     <row r="7" ht="75" spans="1:6">
       <c r="A7" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="B7" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="C7" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="D7" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="E7" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="F7" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="8" ht="45" spans="1:6">
       <c r="A8" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="B8" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="C8" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="D8" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="E8" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="F8" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
     </row>
     <row r="9" ht="45" spans="1:6">
       <c r="A9" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="B9" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="C9" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="D9" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="E9" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="F9" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
     </row>
     <row r="10" ht="58.5" spans="1:6">
       <c r="A10" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="B10" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="C10" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="D10" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="E10" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="F10" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
     </row>
     <row r="11" ht="60" spans="1:6">
       <c r="A11" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="B11" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="C11" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="D11" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="E11" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="F11" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
     </row>
     <row r="12" ht="58.5" spans="1:6">
       <c r="A12" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="B12" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="C12" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="D12" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="E12" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="F12" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:6">
       <c r="A13" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="B13" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="C13" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="D13" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="E13" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="F13" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="14" ht="58.5" spans="1:6">
       <c r="A14" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="B14" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="C14" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="D14" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="E14" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="F14" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
     </row>
     <row r="15" ht="58.5" spans="1:6">
       <c r="A15" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="B15" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="C15" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="D15" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="E15" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="F15" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
     </row>
     <row r="16" ht="58.5" spans="1:6">
       <c r="A16" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="B16" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="C16" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="D16" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="E16" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="F16" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
     </row>
     <row r="17" ht="58.5" spans="1:6">
       <c r="A17" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="B17" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C17" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="D17" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="E17" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="F17" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
     </row>
     <row r="18" ht="58.5" spans="1:6">
       <c r="A18" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="B18" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="C18" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="D18" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="E18" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="F18" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
     </row>
     <row r="19" ht="58.5" spans="1:6">
       <c r="A19" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="B19" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="C19" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="D19" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="E19" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="F19" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
     </row>
     <row r="20" ht="72" spans="1:6">
       <c r="A20" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="B20" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="C20" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="D20" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="E20" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="F20" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
     </row>
     <row r="21" ht="58.5" spans="1:6">
       <c r="A21" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="B21" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="C21" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="D21" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="E21" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="F21" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
     </row>
     <row r="22" ht="58.5" spans="1:6">
       <c r="A22" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="B22" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="C22" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="D22" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="E22" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="F22" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
     </row>
     <row r="23" ht="58.5" spans="1:6">
       <c r="A23" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="B23" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="C23" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="D23" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="E23" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="F23" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
     </row>
     <row r="24" ht="58.5" spans="1:6">
       <c r="A24" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="B24" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="C24" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="D24" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="E24" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="F24" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
     </row>
     <row r="25" ht="90" spans="1:6">
       <c r="A25" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="B25" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="C25" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="D25" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="E25" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="F25" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
     </row>
     <row r="26" ht="58.5" spans="1:6">
       <c r="A26" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="B26" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="C26" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="D26" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="E26" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="F26" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
     </row>
     <row r="27" ht="58.5" spans="1:6">
       <c r="A27" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="B27" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="C27" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="D27" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="E27" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="F27" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
     </row>
     <row r="28" ht="58.5" spans="1:6">
       <c r="A28" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="B28" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="C28" t="s">
+        <v>450</v>
+      </c>
+      <c r="D28" t="s">
         <v>446</v>
       </c>
-      <c r="D28" t="s">
-        <v>442</v>
-      </c>
       <c r="E28" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="F28" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
     </row>
     <row r="29" ht="73.5" spans="1:6">
       <c r="A29" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="B29" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="C29" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="D29" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="E29" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="F29" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
     </row>
     <row r="30" ht="58.5" spans="1:6">
       <c r="A30" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="B30" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="C30" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="D30" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="E30" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="F30" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="B31" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="C31" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="D31" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
     </row>
   </sheetData>
